--- a/data/trans_orig/Q25_A_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2007</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2007 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58234</t>
+          <t>57442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60816</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>86795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120439</t>
+          <t>118797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101213</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>135424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86738</t>
+          <t>88860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105587</t>
+          <t>107169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140137</t>
+          <t>140649</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74308</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29921</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35131</t>
+          <t>35350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>51533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79925</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81839</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>113277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>51271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76184</t>
+          <t>74162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140890</t>
+          <t>138646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179773</t>
+          <t>181477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>59955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90232</t>
+          <t>87414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76570</t>
+          <t>75299</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119399</t>
+          <t>118086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155594</t>
+          <t>157523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62115</t>
+          <t>62656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54283</t>
+          <t>53985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>52617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81653</t>
+          <t>83821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15735</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>59834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91540</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152066</t>
+          <t>153144</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196547</t>
+          <t>196253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189500</t>
+          <t>187394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>238671</t>
+          <t>238140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>203083</t>
+          <t>204423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>251209</t>
+          <t>250531</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>89833</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>123294</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>305080</t>
+          <t>303752</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>362843</t>
+          <t>364803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125205</t>
+          <t>124287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167489</t>
+          <t>166633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108845</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213945</t>
+          <t>211891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265436</t>
+          <t>265948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2012</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2012 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76024</t>
+          <t>76804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>112050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>79186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118571</t>
+          <t>117151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>102431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141404</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152799</t>
+          <t>152587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91656</t>
+          <t>91182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126994</t>
+          <t>127071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34421</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114769</t>
+          <t>115760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>153810</t>
+          <t>156726</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49367</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>78113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>73682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108043</t>
+          <t>108377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50467</t>
+          <t>50766</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65143</t>
+          <t>66205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59429</t>
+          <t>58817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91381</t>
+          <t>91595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132211</t>
+          <t>131409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101937</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138467</t>
+          <t>136167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80293</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111132</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191165</t>
+          <t>190424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240690</t>
+          <t>238273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111775</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148466</t>
+          <t>147956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72977</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102959</t>
+          <t>102184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>191721</t>
+          <t>191639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241182</t>
+          <t>241732</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24411</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39429</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>41520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50443</t>
+          <t>49635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76475</t>
+          <t>76516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41754</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45511</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121860</t>
+          <t>121911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>170120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>142600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195129</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179416</t>
+          <t>180631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230905</t>
+          <t>233647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89270</t>
+          <t>89857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247708</t>
+          <t>247914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>310061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>227904</t>
+          <t>232516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>284809</t>
+          <t>285037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>133430</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173417</t>
+          <t>173771</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>374420</t>
+          <t>379066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>445546</t>
+          <t>447467</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196522</t>
+          <t>195806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>251189</t>
+          <t>249507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121547</t>
+          <t>121524</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161016</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333682</t>
+          <t>333130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398064</t>
+          <t>396541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2016</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2016 (tasa de respuesta: 91,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76011</t>
+          <t>77899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53383</t>
+          <t>53458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81326</t>
+          <t>81154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62117</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89644</t>
+          <t>88709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72005</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102884</t>
+          <t>103049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>49879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78083</t>
+          <t>75567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68533</t>
+          <t>67613</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99988</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49182</t>
+          <t>48590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34770</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59288</t>
+          <t>59076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37567</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,82 +6331,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12761</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>21797</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>61941</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>48169</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>78618</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>10,62%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>6644</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22791</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>61941</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>47570</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>79418</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70775</t>
+          <t>71064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103065</t>
+          <t>102755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37517</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62103</t>
+          <t>62978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115286</t>
+          <t>114597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156087</t>
+          <t>156005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>99328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135267</t>
+          <t>135185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70120</t>
+          <t>71350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180600</t>
+          <t>180399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225598</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85499</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119931</t>
+          <t>121625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>65024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98012</t>
+          <t>96343</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>159087</t>
+          <t>160590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>206048</t>
+          <t>206737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34932</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42067</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67627</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91965</t>
+          <t>91686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>40591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65695</t>
+          <t>65221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109092</t>
+          <t>109765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149808</t>
+          <t>151065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130317</t>
+          <t>130129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176250</t>
+          <t>175211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160454</t>
+          <t>160512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209292</t>
+          <t>208236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>74782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>108811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248121</t>
+          <t>249107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>304897</t>
+          <t>306811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>191292</t>
+          <t>191141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241912</t>
+          <t>241491</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>129398</t>
+          <t>127703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167372</t>
+          <t>167008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332167</t>
+          <t>330662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>394058</t>
+          <t>395363</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139048</t>
+          <t>138957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186498</t>
+          <t>186544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101439</t>
+          <t>101460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138175</t>
+          <t>136942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252786</t>
+          <t>253989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309876</t>
+          <t>309708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2023</t>
+          <t>Población en función del tiempo en años desde que dejó de fumar (cuartiles) en 2023 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46721</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66500</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80128</t>
+          <t>80092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47514</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69850</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>59483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82168</t>
+          <t>82817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>36933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20620</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39585</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143538</t>
+          <t>142895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>42891</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>171658</t>
+          <t>173267</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183767</t>
+          <t>183201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>62010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65178</t>
+          <t>59515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227417</t>
+          <t>228366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154963</t>
+          <t>154443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67133</t>
+          <t>66040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211199</t>
+          <t>211320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76763</t>
+          <t>77452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>461684</t>
+          <t>447513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>71418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>148649</t>
+          <t>148742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>575382</t>
+          <t>576014</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52565</t>
+          <t>53460</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50711</t>
+          <t>49789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73161</t>
+          <t>73746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>48584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42200</t>
+          <t>40927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>29136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41374</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64455</t>
+          <t>64762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36594</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34409</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57232</t>
+          <t>58715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82282</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254673</t>
+          <t>252356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56768</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>77917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>125137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>315310</t>
+          <t>310858</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>79964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279809</t>
+          <t>280654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78043</t>
+          <t>77654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103994</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>151029</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368003</t>
+          <t>367442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65670</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>204453</t>
+          <t>206780</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72311</t>
+          <t>72264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>99285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121208</t>
+          <t>123536</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>293525</t>
+          <t>290975</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120474</t>
+          <t>118685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591547</t>
+          <t>628904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102687</t>
+          <t>100454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215113</t>
+          <t>216470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>772086</t>
+          <t>761106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33655</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57442</t>
+          <t>57274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118797</t>
+          <t>120809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99425</t>
+          <t>101246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135424</t>
+          <t>134851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88860</t>
+          <t>87363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119418</t>
+          <t>120354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107169</t>
+          <t>106518</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140649</t>
+          <t>140272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58968</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74037</t>
+          <t>74085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>33998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60992</t>
+          <t>60029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51533</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>79244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83818</t>
+          <t>82694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>114394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74162</t>
+          <t>75103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138646</t>
+          <t>142157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181477</t>
+          <t>179245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>61276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>88591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>52848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>76477</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>120606</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>157523</t>
+          <t>157578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17791</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19273</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35011</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>54100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83821</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59834</t>
+          <t>58464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93036</t>
+          <t>93149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153144</t>
+          <t>151283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196253</t>
+          <t>195034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>189501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>238140</t>
+          <t>238832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>204423</t>
+          <t>204037</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>250531</t>
+          <t>251539</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89833</t>
+          <t>91249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>303752</t>
+          <t>306450</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>364803</t>
+          <t>364462</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124287</t>
+          <t>126793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166633</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>79418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>109802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211891</t>
+          <t>213966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265948</t>
+          <t>266848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>76530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112050</t>
+          <t>112885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79186</t>
+          <t>79884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117151</t>
+          <t>117744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102431</t>
+          <t>100630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140118</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112037</t>
+          <t>112772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152587</t>
+          <t>151644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91182</t>
+          <t>90519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127071</t>
+          <t>128268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115760</t>
+          <t>112732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>156726</t>
+          <t>153104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48264</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78113</t>
+          <t>77778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>37265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73682</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108377</t>
+          <t>107482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>49132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36826</t>
+          <t>37411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>66206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50956</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82879</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32267</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91595</t>
+          <t>90490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131409</t>
+          <t>133452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99983</t>
+          <t>101229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136167</t>
+          <t>137137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79789</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111172</t>
+          <t>111865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190424</t>
+          <t>192069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>238256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111027</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147956</t>
+          <t>146934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>71343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102184</t>
+          <t>102051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>191639</t>
+          <t>190716</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241732</t>
+          <t>239532</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>27892</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24317</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41520</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49635</t>
+          <t>50200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>75607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21884</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>42601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>45529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71842</t>
+          <t>71788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121911</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170120</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>33108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142600</t>
+          <t>141344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194617</t>
+          <t>192631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180631</t>
+          <t>179188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233647</t>
+          <t>231088</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58551</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89857</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247914</t>
+          <t>247177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310061</t>
+          <t>307876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>232516</t>
+          <t>232320</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>286406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>132369</t>
+          <t>136168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173771</t>
+          <t>172691</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>379066</t>
+          <t>376453</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>442840</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195806</t>
+          <t>197477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249507</t>
+          <t>249396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>123096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>161109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>334545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396541</t>
+          <t>403641</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77899</t>
+          <t>75706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53458</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>82238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>61769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88709</t>
+          <t>88820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103049</t>
+          <t>103469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49879</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75567</t>
+          <t>75473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67613</t>
+          <t>68378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97320</t>
+          <t>97586</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48590</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65267</t>
+          <t>63267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78618</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>71904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>103836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62978</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114597</t>
+          <t>115685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156005</t>
+          <t>156876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99328</t>
+          <t>99794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135185</t>
+          <t>134985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71350</t>
+          <t>72015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180399</t>
+          <t>179968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228376</t>
+          <t>227932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>83700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121625</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65024</t>
+          <t>66765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96343</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160590</t>
+          <t>158054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>206737</t>
+          <t>205882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41261</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>68155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50077</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62756</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91686</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>38618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65221</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109765</t>
+          <t>109901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151065</t>
+          <t>151999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130129</t>
+          <t>128896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175211</t>
+          <t>175696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160512</t>
+          <t>164138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208236</t>
+          <t>208859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108811</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249107</t>
+          <t>246115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306811</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>191141</t>
+          <t>191743</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241491</t>
+          <t>240442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127703</t>
+          <t>128616</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167008</t>
+          <t>168010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>330662</t>
+          <t>330599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>395363</t>
+          <t>395339</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138957</t>
+          <t>140477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186544</t>
+          <t>186040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101460</t>
+          <t>99856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>137133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253989</t>
+          <t>252977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309708</t>
+          <t>312026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66970</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>60904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80092</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57688</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69051</t>
+          <t>73235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70475</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59483</t>
+          <t>64018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82817</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36933</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>38278</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46938</t>
+          <t>48047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>21318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>161431</t>
+          <t>171712</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161431</t>
+          <t>171712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161431</t>
+          <t>171712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>203748</t>
+          <t>216544</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203748</t>
+          <t>216544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203748</t>
+          <t>216544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74330</t>
+          <t>82058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>142895</t>
+          <t>97197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>48326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>109882</t>
+          <t>120638</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>101695</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>173267</t>
+          <t>137353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95488</t>
+          <t>105234</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183201</t>
+          <t>122641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51213</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>44135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146701</t>
+          <t>160013</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>141043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228366</t>
+          <t>180705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80669</t>
+          <t>89901</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>74047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154443</t>
+          <t>108080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54326</t>
+          <t>58387</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43633</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>70830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>134995</t>
+          <t>148289</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>129488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211320</t>
+          <t>169471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>291142</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77452</t>
+          <t>39415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>447513</t>
+          <t>66817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47744</t>
+          <t>55590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71418</t>
+          <t>80596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>350284</t>
+          <t>119969</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>148742</t>
+          <t>102252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>576014</t>
+          <t>141378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>541629</t>
+          <t>329825</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>541629</t>
+          <t>329825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>541629</t>
+          <t>329825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>219083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>219083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>219083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>741862</t>
+          <t>548909</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>741862</t>
+          <t>548909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>741862</t>
+          <t>548909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>46503</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53460</t>
+          <t>57228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>68382</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49789</t>
+          <t>57086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>81334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>40926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48584</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>29508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33614</t>
+          <t>37811</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>70433</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>58520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79272</t>
+          <t>84297</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40927</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>57209</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40128</t>
+          <t>45237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>70395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>39778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34473</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>61642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136893</t>
+          <t>148632</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136893</t>
+          <t>148632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136893</t>
+          <t>148632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86456</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86456</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86456</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>223350</t>
+          <t>243498</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>223350</t>
+          <t>243498</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>223350</t>
+          <t>243498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>173448</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62409</t>
+          <t>166631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>252356</t>
+          <t>211440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66255</t>
+          <t>73018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55076</t>
+          <t>60490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77917</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>239703</t>
+          <t>261051</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125137</t>
+          <t>234574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>310858</t>
+          <t>284518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>191741</t>
+          <t>208390</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79964</t>
+          <t>186904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280654</t>
+          <t>233172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>98102</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77654</t>
+          <t>85442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102879</t>
+          <t>112422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>282179</t>
+          <t>306493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151029</t>
+          <t>281434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367442</t>
+          <t>334777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>138650</t>
+          <t>152333</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>130030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>206780</t>
+          <t>174154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84915</t>
+          <t>91443</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72264</t>
+          <t>77517</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99285</t>
+          <t>106062</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>223564</t>
+          <t>243776</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123536</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>290975</t>
+          <t>272066</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118685</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>628904</t>
+          <t>120168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87399</t>
+          <t>96218</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>82521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100454</t>
+          <t>111045</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>423513</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216470</t>
+          <t>172628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>761106</t>
+          <t>224037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>650169</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>650169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>650169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>329007</t>
+          <t>358781</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>329007</t>
+          <t>358781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329007</t>
+          <t>358781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1168960</t>
+          <t>1008950</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1168960</t>
+          <t>1008950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1168960</t>
+          <t>1008950</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
